--- a/listas_precios/listas_colocacion.xlsx
+++ b/listas_precios/listas_colocacion.xlsx
@@ -1,41 +1,86 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24729"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\APP PARABRISAS\listas_precios\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76D2B80F-54D1-44C7-B83A-6AA504F8A677}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
-  <si>
-    <t>tipo</t>
-  </si>
-  <si>
-    <t>precio</t>
-  </si>
-  <si>
-    <t>parabrisas</t>
-  </si>
-  <si>
-    <t>luneta</t>
-  </si>
-  <si>
-    <t>vidrio de puerta</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+  <si>
+    <t>ALETADELANTERA</t>
+  </si>
+  <si>
+    <t>COLOC. ALETA DEL. EN CARROCERIA EJ P308 ETC</t>
+  </si>
+  <si>
+    <t>CAMIONBTE</t>
+  </si>
+  <si>
+    <t>COLOCACION DE PSAS CAMION CON BTE</t>
+  </si>
+  <si>
+    <t>CAMIONPEG</t>
+  </si>
+  <si>
+    <t>COLOCACION DE PSA CAMION PEGADO</t>
+  </si>
+  <si>
+    <t>CUSTODIATRASERA</t>
+  </si>
+  <si>
+    <t>COLOCACION CUSTODIA TRASERA PEGADA</t>
+  </si>
+  <si>
+    <t>LUNETA</t>
+  </si>
+  <si>
+    <t>COLOCACION LUNETA PEGADA</t>
+  </si>
+  <si>
+    <t>PARABRISAS</t>
+  </si>
+  <si>
+    <t>COLOCACION PARABRISAS PEGADO</t>
+  </si>
+  <si>
+    <t>PARABRISASBTE</t>
+  </si>
+  <si>
+    <t>COLOCACION PARABRISA-LUNETA CON BURLETE</t>
+  </si>
+  <si>
+    <t>PUERTA</t>
+  </si>
+  <si>
+    <t>COLOCACION VIDRIO PUERTA</t>
+  </si>
+  <si>
+    <t>VENTANA</t>
+  </si>
+  <si>
+    <t>COLOCACION VENTANA C/BISAGRAS</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -44,12 +89,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <sz val="10"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="2">
@@ -60,7 +101,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -68,41 +109,34 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{CAA051D1-0F6D-4F06-B26B-3969D511A5FA}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -144,7 +178,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -176,9 +210,27 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -210,6 +262,24 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -385,40 +455,111 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="47.7109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" t="s">
+      <c r="C1" s="1">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
+      <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" t="s">
+      <c r="C2" s="1">
+        <v>33567</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B4">
-        <v>0</v>
+      <c r="B3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="1">
+        <v>57575.57</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="1">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="1">
+        <v>30840.68</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="1">
+        <v>42121.49</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="1">
+        <v>24811</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="1">
+        <v>13781.68</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="1">
+        <v>15442.12</v>
       </c>
     </row>
   </sheetData>

--- a/listas_precios/listas_colocacion.xlsx
+++ b/listas_precios/listas_colocacion.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\APP PARABRISAS\listas_precios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76D2B80F-54D1-44C7-B83A-6AA504F8A677}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0987A2B9-2CD7-418E-88E2-3B7ED97DBA8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,60 +20,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
-  <si>
-    <t>ALETADELANTERA</t>
-  </si>
-  <si>
-    <t>COLOC. ALETA DEL. EN CARROCERIA EJ P308 ETC</t>
-  </si>
-  <si>
-    <t>CAMIONBTE</t>
-  </si>
-  <si>
-    <t>COLOCACION DE PSAS CAMION CON BTE</t>
-  </si>
-  <si>
-    <t>CAMIONPEG</t>
-  </si>
-  <si>
-    <t>COLOCACION DE PSA CAMION PEGADO</t>
-  </si>
-  <si>
-    <t>CUSTODIATRASERA</t>
-  </si>
-  <si>
-    <t>COLOCACION CUSTODIA TRASERA PEGADA</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>LUNETA</t>
-  </si>
-  <si>
-    <t>COLOCACION LUNETA PEGADA</t>
   </si>
   <si>
     <t>PARABRISAS</t>
   </si>
   <si>
-    <t>COLOCACION PARABRISAS PEGADO</t>
-  </si>
-  <si>
-    <t>PARABRISASBTE</t>
-  </si>
-  <si>
-    <t>COLOCACION PARABRISA-LUNETA CON BURLETE</t>
-  </si>
-  <si>
-    <t>PUERTA</t>
-  </si>
-  <si>
-    <t>COLOCACION VIDRIO PUERTA</t>
-  </si>
-  <si>
-    <t>VENTANA</t>
-  </si>
-  <si>
-    <t>COLOCACION VENTANA C/BISAGRAS</t>
+    <t>VIDRIO DE PUERTA</t>
   </si>
 </sst>
 </file>
@@ -456,110 +411,34 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="47.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="1">
+        <v>30840.68</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1">
-        <v>18000</v>
+      <c r="B2" s="1">
+        <v>42121.49</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="1">
-        <v>33567</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="1">
-        <v>57575.57</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="1">
-        <v>18000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="1">
-        <v>30840.68</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="1">
-        <v>42121.49</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="1">
-        <v>24811</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="1">
+      <c r="B3" s="1">
         <v>13781.68</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="1">
-        <v>15442.12</v>
       </c>
     </row>
   </sheetData>
